--- a/KURIKULUM2026_REVISI/009_LANGKAH2_CPL_FORMAL.xlsx
+++ b/KURIKULUM2026_REVISI/009_LANGKAH2_CPL_FORMAL.xlsx
@@ -1087,7 +1087,7 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>KK1–KK6 — AI, Data, Cloud/IoT, GRC, Platform UI/UX, Startup, Pemetaan 19 BoK IS2020 &amp; 14 BoK IT2017.</t>
+          <t>KK1–KK6 — AI, Data, Cloud/IoT, GRC, Platform UI/UX, Startup, Pemetaan 21 BoK IS2020 &amp; 15 BoK IT2017.</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Kompilasi Master Matriks 14 CPL ↔ 19 BoK IS ↔ 14 BoK IT ↔ 4 PL ↔ 3 Peminatan ↔ VMTS 2045.</t>
+          <t>Kompilasi Master Matriks 14 CPL ↔ 21 BoK IS ↔ 15 BoK IT ↔ 4 PL ↔ 3 Peminatan ↔ VMTS 2045.</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>19 BoK IS2020 + 14 BoK IT2017 terpetakan penuh</t>
+          <t>21 BoK IS2020 + 15 BoK IT2017 terpetakan penuh, mencakup seluruh BK kompetensi utama wajib</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>Standar Kurikulum Sistem Informasi, 17 CPL-P, 17 CPL-K, dan 19 Bahan Kajian.</t>
+          <t>Standar Kurikulum Sistem Informasi: 17 CPL-P, 17 CPL-K, dan 19 Bahan Kajian master (11 kompetensi utama wajib diadopsi + 1 umum + 7 pendukung).</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Standar Kurikulum Teknologi Informasi, Infrastruktur, Cloud, Cybersecurity, dan IoT.</t>
+          <t>Standar Kurikulum Teknologi Informasi: 27 Bahan Kajian master (14 penciri utama wajib diadopsi + 13 penciri pendukung), Infrastruktur, Cloud, Cybersecurity, IoT, dan Praktek Profesional Global.</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Detail 14 CPL, Genealogi Sumber, 19 BoK IS &amp; 14 BoK IT.</t>
+          <t>Detail 14 CPL, Genealogi Sumber, 21 BoK IS &amp; 15 BoK IT.</t>
         </is>
       </c>
     </row>
